--- a/src/test/resources/testdata/TestData.xlsx
+++ b/src/test/resources/testdata/TestData.xlsx
@@ -8,13 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2480269\Downloads\demo\mediconnect-automation\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53E8CCDA-620B-4BA0-AD1B-843DDE258337}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03DB0315-67C0-4FBC-B012-A56B4FF9B4C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{20EC9760-B52E-4482-B97D-09277A4A575D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="8" activeTab="10" xr2:uid="{20EC9760-B52E-4482-B97D-09277A4A575D}"/>
   </bookViews>
   <sheets>
     <sheet name="Logins" sheetId="1" r:id="rId1"/>
     <sheet name="PatientRegister" sheetId="2" r:id="rId2"/>
+    <sheet name="AddPatient" sheetId="3" r:id="rId3"/>
+    <sheet name="NewAppointment" sheetId="4" r:id="rId4"/>
+    <sheet name="RequestLabTest" sheetId="5" r:id="rId5"/>
+    <sheet name="NewRecord" sheetId="6" r:id="rId6"/>
+    <sheet name="ScheduleSession" sheetId="7" r:id="rId7"/>
+    <sheet name="AddItem" sheetId="8" r:id="rId8"/>
+    <sheet name="AiAssistant" sheetId="9" r:id="rId9"/>
+    <sheet name="DoctorRegister" sheetId="10" r:id="rId10"/>
+    <sheet name="DoctorLogin" sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="108">
   <si>
     <t>testId</t>
   </si>
@@ -96,6 +105,9 @@
     <t>TP001_patient_register</t>
   </si>
   <si>
+    <t>Auto</t>
+  </si>
+  <si>
     <t>Password@1</t>
   </si>
   <si>
@@ -175,13 +187,199 @@
   </si>
   <si>
     <t>Priya@9012</t>
+  </si>
+  <si>
+    <t>age</t>
+  </si>
+  <si>
+    <t>emergencyContact</t>
+  </si>
+  <si>
+    <t>DPA001_add_patient</t>
+  </si>
+  <si>
+    <t>auto_patient_${UNIQUE}@test.com</t>
+  </si>
+  <si>
+    <t>Patient@1234</t>
+  </si>
+  <si>
+    <t>Emergency - 8888888888</t>
+  </si>
+  <si>
+    <t>patientSearchQuery</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>time</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>DAP001_new_appointment</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>11:30AM</t>
+  </si>
+  <si>
+    <t>In-person</t>
+  </si>
+  <si>
+    <t>Pending</t>
+  </si>
+  <si>
+    <t>testType</t>
+  </si>
+  <si>
+    <t>priority</t>
+  </si>
+  <si>
+    <t>requestedDate</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>DLR001_request_test</t>
+  </si>
+  <si>
+    <t>CBC</t>
+  </si>
+  <si>
+    <t>Routine</t>
+  </si>
+  <si>
+    <t>Automated test request — please ignore</t>
+  </si>
+  <si>
+    <t>recordDate</t>
+  </si>
+  <si>
+    <t>diagnosis</t>
+  </si>
+  <si>
+    <t>treatment</t>
+  </si>
+  <si>
+    <t>prescription</t>
+  </si>
+  <si>
+    <t>clinicalNotes</t>
+  </si>
+  <si>
+    <t>DMR001_new_record</t>
+  </si>
+  <si>
+    <t>Automated test diagnosis - routine check</t>
+  </si>
+  <si>
+    <t>Rest, hydration, follow-up in 7 days</t>
+  </si>
+  <si>
+    <t>Paracetamol | 500mg | 1-0-1</t>
+  </si>
+  <si>
+    <t>Created by Selenium automation suite</t>
+  </si>
+  <si>
+    <t>duration</t>
+  </si>
+  <si>
+    <t>reason</t>
+  </si>
+  <si>
+    <t>DTM001_schedule_session</t>
+  </si>
+  <si>
+    <t>Automated test - follow up consultation</t>
+  </si>
+  <si>
+    <t>itemName</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>quantity</t>
+  </si>
+  <si>
+    <t>reorderLevel</t>
+  </si>
+  <si>
+    <t>DSC001_add_item</t>
+  </si>
+  <si>
+    <t>Paracetamol ${UNIQUE}</t>
+  </si>
+  <si>
+    <t>Medication</t>
+  </si>
+  <si>
+    <t>question</t>
+  </si>
+  <si>
+    <t>DAI001_normal_range</t>
+  </si>
+  <si>
+    <t>What is the normal range for HbA1c?</t>
+  </si>
+  <si>
+    <t>DAI002_drug_dose</t>
+  </si>
+  <si>
+    <t>Common side effects of Lisinopril</t>
+  </si>
+  <si>
+    <t>DAI003_lab_interpret</t>
+  </si>
+  <si>
+    <t>How to interpret a BNP result?</t>
+  </si>
+  <si>
+    <t>specialization</t>
+  </si>
+  <si>
+    <t>hospital</t>
+  </si>
+  <si>
+    <t>TD001_doctor_register</t>
+  </si>
+  <si>
+    <t>Doctor${UNIQUE}</t>
+  </si>
+  <si>
+    <t>auto.doctor.${UNIQUE}@test.com</t>
+  </si>
+  <si>
+    <t>Cardiology</t>
+  </si>
+  <si>
+    <t>Test Hospital</t>
+  </si>
+  <si>
+    <t>TC_DOC_LOGIN_VALID</t>
+  </si>
+  <si>
+    <t>arun.kumar@cgh.com</t>
+  </si>
+  <si>
+    <t>MediConnect@123</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -199,6 +397,14 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -263,24 +469,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -694,6 +901,115 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87715164-B4A9-4967-BE68-FEBD691217EB}">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E2" s="8">
+        <v>9876543210</v>
+      </c>
+      <c r="F2" t="s">
+        <v>103</v>
+      </c>
+      <c r="G2" t="s">
+        <v>104</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E80DC387-7ADE-42F2-AD04-E9AC427B8F77}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="19.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>107</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC5547E1-8265-48F6-A84D-52EAF56CC962}">
   <dimension ref="A1:I5"/>
@@ -717,7 +1033,7 @@
         <v>12</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>1</v>
@@ -743,42 +1059,42 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="10" t="s">
         <v>23</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>22</v>
       </c>
       <c r="E2" s="9">
         <v>9876543210</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="I2" s="8" t="s">
         <v>19</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E3" s="11">
         <v>9123456701</v>
@@ -787,27 +1103,27 @@
         <v>3121988</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E4" s="4">
         <v>9123456702</v>
@@ -816,27 +1132,27 @@
         <v>3121988</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E5" s="4">
         <v>9123456702</v>
@@ -845,13 +1161,13 @@
         <v>3121988</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -860,4 +1176,439 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E08C65E8-DE7E-42A4-B37E-94981247A45D}">
+  <dimension ref="A1:K2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I1" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J1" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1" s="13" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E2" s="8">
+        <v>9999999999</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G2">
+        <v>30</v>
+      </c>
+      <c r="H2" s="8">
+        <v>34700</v>
+      </c>
+      <c r="I2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5BE7F55-1345-4108-923B-0A41576493AB}">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="22.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" s="8">
+        <v>46188</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2D9C8C5-C73D-486C-8F51-3D510C42F653}">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="33.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E2" s="8">
+        <v>46188</v>
+      </c>
+      <c r="F2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FFAC5E4-BDFE-4DC7-B957-884FFA341B3B}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="31.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" s="8">
+        <v>46188</v>
+      </c>
+      <c r="D2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97E58940-03EA-43D5-AB8A-F1428AB480A3}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="22.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="7.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.6328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="31.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" s="8">
+        <v>46188</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E2">
+        <v>30</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8D8907D-C1D4-4085-BA57-C8F8A8DB6768}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="15.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D2">
+        <v>100</v>
+      </c>
+      <c r="E2">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1DC6E31-8F32-4B15-972B-7124E1050FED}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/test/resources/testdata/TestData.xlsx
+++ b/src/test/resources/testdata/TestData.xlsx
@@ -481,6 +481,9 @@
     <sheet name="SupplyOrders" sheetId="8" r:id="rId10"/>
     <sheet name="TelemedicineSessions" sheetId="9" r:id="rId11"/>
     <sheet name="AnalyticsFilters" sheetId="10" r:id="rId12"/>
+    <sheet name="PatientBookings" sheetId="11" r:id="rId13"/>
+    <sheet name="LabReportAIQuestions" sheetId="12" r:id="rId14"/>
+    <sheet name="AiAssistantInteractions" sheetId="13" r:id="rId15"/>
   </sheets>
   <calcPr fullPrecision="1" calcId="125725"/>
 </workbook>
@@ -749,6 +752,481 @@
       <c r="D6" t="inlineStr">
         <is>
           <t>Last 30 Days</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl\worksheets\sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>testId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>doctor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TBA001_arun_inperson</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dr. Arun Kumar — Cardiology</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>10:00 AM</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Cardiology follow-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>TBA002_meena_video</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dr. Meena Reddy — Neurology</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>11:00 AM</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Video</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Neurology consultation</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TBA003_vikram_inperson</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dr. Vikram Singh — Orthopedics</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2:00 PM</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knee pain checkup</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl\worksheets\sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>testId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>question</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>mode</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TQ001_chip_ldl</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>What is LDL cholesterol?</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>chip</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>TQ002_chip_lower_ldl</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>How to lower LDL naturally?</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>chip</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TQ003_chip_statins</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>What are statins?</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>chip</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TQ004_chip_ecg</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Is my ECG result good?</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>chip</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TQ005_type_hdl</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>What does HDL mean?</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TQ006_type_blood_test</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Explain my blood test results</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl\worksheets\sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>testId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>mode</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TAH001_chip_lipid</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>General Chat</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>chip</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Explain my lipid panel results</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>TAH002_chip_ldl</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>General Chat</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>chip</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>What does elevated LDL mean?</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TAH003_type_cholesterol</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>General Chat</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>What are normal cholesterol levels?</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TAH004_type_symptoms</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Symptom Checker</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>I have a headache and fever for 2 days</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TAH005_quick_symptom</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>quickAction</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Symptom Checker</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TAH006_quick_lab</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>quickAction</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Explain My Lab Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TAH007_common_bp</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>commonQuestion</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>What does my blood pressure reading mean?</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TAH008_common_diabetes</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>commonQuestion</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>How can I manage my diabetes better?</t>
         </is>
       </c>
     </row>

--- a/src/test/resources/testdata/TestData.xlsx
+++ b/src/test/resources/testdata/TestData.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B4F03BB-B6C3-4B2C-8029-DEFAD413489A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="21" activeTab="23" xr2:uid="{20EC9760-B52E-4482-B97D-09277A4A575D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="3" activeTab="22" xr2:uid="{20EC9760-B52E-4482-B97D-09277A4A575D}"/>
   </bookViews>
   <sheets>
     <sheet name="Logins" sheetId="1" r:id="rId1"/>

--- a/src/test/resources/testdata/TestData.xlsx
+++ b/src/test/resources/testdata/TestData.xlsx
@@ -1,14 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30117"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30117"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F1D512F5-6DAD-465E-ADA3-9F75485252ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2480269\Downloads\demo\mediconnect-automation\src\test\resources\testdata\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C96CBA69-494A-4A81-AE2D-D83522FBBE10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="22" activeTab="2" xr2:uid="{20EC9760-B52E-4482-B97D-09277A4A575D}"/>
   </bookViews>
   <sheets>
-    <sheet name="AdminRegistration" sheetId="1" r:id="rId1"/>
+    <sheet name="Logins" sheetId="1" r:id="rId1"/>
+    <sheet name="PatientRegister" sheetId="2" r:id="rId2"/>
+    <sheet name="AdminRegistration" sheetId="12" r:id="rId3"/>
+    <sheet name="Sheet12" sheetId="13" r:id="rId4"/>
+    <sheet name="AddPatient" sheetId="3" r:id="rId5"/>
+    <sheet name="NewAppointment" sheetId="4" r:id="rId6"/>
+    <sheet name="RequestLabTest" sheetId="5" r:id="rId7"/>
+    <sheet name="NewRecord" sheetId="6" r:id="rId8"/>
+    <sheet name="ScheduleSession" sheetId="7" r:id="rId9"/>
+    <sheet name="AddItem" sheetId="8" r:id="rId10"/>
+    <sheet name="AiAssistant" sheetId="9" r:id="rId11"/>
+    <sheet name="DoctorRegister" sheetId="10" r:id="rId12"/>
+    <sheet name="DoctorLogin" sheetId="11" r:id="rId13"/>
+    <sheet name="Hospitals" sheetId="14" r:id="rId14"/>
+    <sheet name="Appointments" sheetId="15" r:id="rId15"/>
+    <sheet name="NewAppointments" sheetId="16" r:id="rId16"/>
+    <sheet name="DiagnosticsSearch" sheetId="17" r:id="rId17"/>
+    <sheet name="DiagnosticsStatus" sheetId="18" r:id="rId18"/>
+    <sheet name="SupplyOrders" sheetId="19" r:id="rId19"/>
+    <sheet name="TelemedicineSessions" sheetId="20" r:id="rId20"/>
+    <sheet name="AnalyticsFilters" sheetId="21" r:id="rId21"/>
+    <sheet name="PatientBookings" sheetId="22" r:id="rId22"/>
+    <sheet name="LabReportAIQuestions" sheetId="23" r:id="rId23"/>
+    <sheet name="AiAssistantInteractions" sheetId="24" r:id="rId24"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -26,12 +54,150 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="267">
+  <si>
+    <t>testId</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>password</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC004_doctor_valid  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">shifani@doctor.com   </t>
+  </si>
+  <si>
+    <t>shifanidoctor@134</t>
+  </si>
+  <si>
+    <t>TC006_invalid_format</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shifanidoctor  </t>
+  </si>
+  <si>
+    <t>anything</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC072_wrong_creds </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> wrong@user.com </t>
+  </si>
+  <si>
+    <t>WrongPass123</t>
+  </si>
+  <si>
+    <t>firstName</t>
+  </si>
+  <si>
+    <t>lastName</t>
+  </si>
+  <si>
+    <t>phone</t>
+  </si>
+  <si>
+    <t>dateOfBirth</t>
+  </si>
+  <si>
+    <t>bloodGroup</t>
+  </si>
+  <si>
+    <t>gender</t>
+  </si>
+  <si>
+    <t>TP001_patient_register</t>
+  </si>
+  <si>
+    <t>Samridhan</t>
+  </si>
+  <si>
+    <t>Patient${UNIQUE}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">auto.patient.${UNIQUE}@test.com	</t>
+  </si>
+  <si>
+    <t>342005</t>
+  </si>
+  <si>
+    <t>O-</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>Password@1</t>
+  </si>
+  <si>
+    <t>TP002_patient_register</t>
+  </si>
+  <si>
+    <t>Shifani</t>
+  </si>
+  <si>
+    <t>Joseph${UNIQUE}</t>
+  </si>
+  <si>
+    <t>maya.sharma.${UNIQUE}@test.com</t>
+  </si>
+  <si>
+    <t>O+</t>
+  </si>
+  <si>
+    <t>Maya@1234</t>
+  </si>
+  <si>
+    <t>TP003_patient_register</t>
+  </si>
+  <si>
+    <t>Abhiram</t>
+  </si>
+  <si>
+    <t>Kapoor${UNIQUE}</t>
+  </si>
+  <si>
+    <t>rohan.kapoor.${UNIQUE}@test.com</t>
+  </si>
+  <si>
+    <t>A+</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>Rohan@5678</t>
+  </si>
+  <si>
+    <t>TP004_patient_register</t>
+  </si>
+  <si>
+    <t>Chandrakanth</t>
+  </si>
+  <si>
+    <t>Iyer${UNIQUE}</t>
+  </si>
+  <si>
+    <t>priya.iyer.${UNIQUE}@test.com</t>
+  </si>
+  <si>
+    <t>AB+</t>
+  </si>
+  <si>
+    <t>Priya@9012</t>
+  </si>
   <si>
     <t>Hospital</t>
   </si>
@@ -48,44 +214,662 @@
     <t>phone number</t>
   </si>
   <si>
-    <t>password</t>
-  </si>
-  <si>
     <t>confirm password</t>
   </si>
   <si>
     <t>Cognizant Hospitals</t>
   </si>
   <si>
-    <t>Neo</t>
-  </si>
-  <si>
-    <t>Anderson</t>
-  </si>
-  <si>
-    <t>neo@matrix.com</t>
+    <t xml:space="preserve">Obi </t>
+  </si>
+  <si>
+    <t>Kenobi</t>
+  </si>
+  <si>
+    <t>wan@kenobi.com</t>
   </si>
   <si>
     <t>Matrix@reloaded</t>
   </si>
   <si>
-    <t>Anakin</t>
-  </si>
-  <si>
-    <t>Skywalker</t>
-  </si>
-  <si>
-    <t>c3po@tatooin.com</t>
+    <t>Darth</t>
+  </si>
+  <si>
+    <t>Vader</t>
+  </si>
+  <si>
+    <t>darth@vader.in</t>
   </si>
   <si>
     <t>r2d2!!</t>
+  </si>
+  <si>
+    <t>age</t>
+  </si>
+  <si>
+    <t>emergencyContact</t>
+  </si>
+  <si>
+    <t>DPA001_add_patient</t>
+  </si>
+  <si>
+    <t>Auto</t>
+  </si>
+  <si>
+    <t>auto_patient_${UNIQUE}@test.com</t>
+  </si>
+  <si>
+    <t>Patient@1234</t>
+  </si>
+  <si>
+    <t>Emergency - 8888888888</t>
+  </si>
+  <si>
+    <t>patientSearchQuery</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>time</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>DAP001_new_appointment</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>11:30AM</t>
+  </si>
+  <si>
+    <t>In-person</t>
+  </si>
+  <si>
+    <t>Pending</t>
+  </si>
+  <si>
+    <t>testType</t>
+  </si>
+  <si>
+    <t>priority</t>
+  </si>
+  <si>
+    <t>requestedDate</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>DLR001_request_test</t>
+  </si>
+  <si>
+    <t>CBC</t>
+  </si>
+  <si>
+    <t>Routine</t>
+  </si>
+  <si>
+    <t>Automated test request — please ignore</t>
+  </si>
+  <si>
+    <t>recordDate</t>
+  </si>
+  <si>
+    <t>diagnosis</t>
+  </si>
+  <si>
+    <t>treatment</t>
+  </si>
+  <si>
+    <t>prescription</t>
+  </si>
+  <si>
+    <t>clinicalNotes</t>
+  </si>
+  <si>
+    <t>DMR001_new_record</t>
+  </si>
+  <si>
+    <t>Automated test diagnosis - routine check</t>
+  </si>
+  <si>
+    <t>Rest, hydration, follow-up in 7 days</t>
+  </si>
+  <si>
+    <t>Paracetamol | 500mg | 1-0-1</t>
+  </si>
+  <si>
+    <t>Created by Selenium automation suite</t>
+  </si>
+  <si>
+    <t>duration</t>
+  </si>
+  <si>
+    <t>reason</t>
+  </si>
+  <si>
+    <t>DTM001_schedule_session</t>
+  </si>
+  <si>
+    <t>Automated test - follow up consultation</t>
+  </si>
+  <si>
+    <t>itemName</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>quantity</t>
+  </si>
+  <si>
+    <t>reorderLevel</t>
+  </si>
+  <si>
+    <t>DSC001_add_item</t>
+  </si>
+  <si>
+    <t>Paracetamol ${UNIQUE}</t>
+  </si>
+  <si>
+    <t>Medication</t>
+  </si>
+  <si>
+    <t>question</t>
+  </si>
+  <si>
+    <t>DAI001_normal_range</t>
+  </si>
+  <si>
+    <t>What is the normal range for HbA1c?</t>
+  </si>
+  <si>
+    <t>DAI002_drug_dose</t>
+  </si>
+  <si>
+    <t>Common side effects of Lisinopril</t>
+  </si>
+  <si>
+    <t>DAI003_lab_interpret</t>
+  </si>
+  <si>
+    <t>How to interpret a BNP result?</t>
+  </si>
+  <si>
+    <t>specialization</t>
+  </si>
+  <si>
+    <t>hospital</t>
+  </si>
+  <si>
+    <t>TD001_doctor_register</t>
+  </si>
+  <si>
+    <t>Doctor${UNIQUE}</t>
+  </si>
+  <si>
+    <t>auto.doctor.${UNIQUE}@test.com</t>
+  </si>
+  <si>
+    <t>Cardiology</t>
+  </si>
+  <si>
+    <t>Test Hospital</t>
+  </si>
+  <si>
+    <t>TC_DOC_LOGIN_VALID</t>
+  </si>
+  <si>
+    <t>arun.kumar@cgh.com</t>
+  </si>
+  <si>
+    <t>MediConnect@123</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>city</t>
+  </si>
+  <si>
+    <t>address</t>
+  </si>
+  <si>
+    <t>totalBeds</t>
+  </si>
+  <si>
+    <t>availableBeds</t>
+  </si>
+  <si>
+    <t>TH001_add_chennai</t>
+  </si>
+  <si>
+    <t>MGM Hospital ${UNIQUE}</t>
+  </si>
+  <si>
+    <t>Chennai</t>
+  </si>
+  <si>
+    <t>123 Test Street</t>
+  </si>
+  <si>
+    <t>TH002_add_mumbai</t>
+  </si>
+  <si>
+    <t>Mumbai Care ${UNIQUE}</t>
+  </si>
+  <si>
+    <t>Mumbai</t>
+  </si>
+  <si>
+    <t>45 Marine Drive</t>
+  </si>
+  <si>
+    <t>TH003_add_delhi</t>
+  </si>
+  <si>
+    <t>Delhi Health ${UNIQUE}</t>
+  </si>
+  <si>
+    <t>Delhi</t>
+  </si>
+  <si>
+    <t>200 Connaught Place</t>
+  </si>
+  <si>
+    <t>doctor</t>
+  </si>
+  <si>
+    <t>TA001_arun_city_jun01</t>
+  </si>
+  <si>
+    <t>Dr. Arun Kumar</t>
+  </si>
+  <si>
+    <t>City General Hospital</t>
+  </si>
+  <si>
+    <t>TA002_meena_apollo_jun15</t>
+  </si>
+  <si>
+    <t>Dr. Meena Reddy</t>
+  </si>
+  <si>
+    <t>Apollo Medical Centre</t>
+  </si>
+  <si>
+    <t>TA003_vikram_medicare_jul01</t>
+  </si>
+  <si>
+    <t>Dr. Vikram Singh</t>
+  </si>
+  <si>
+    <t>MediCare Specialty Hospital</t>
+  </si>
+  <si>
+    <t>TA004_priya_city_aug20</t>
+  </si>
+  <si>
+    <t>Dr. Priya Sharma</t>
+  </si>
+  <si>
+    <t>TA005_lakshmi_apollo_sep10</t>
+  </si>
+  <si>
+    <t>Dr. Lakshmi Nair</t>
+  </si>
+  <si>
+    <t>patient</t>
+  </si>
+  <si>
+    <t>TN001_rajesh_arun_city</t>
+  </si>
+  <si>
+    <t>PT-0001 — Rajesh Sharma</t>
+  </si>
+  <si>
+    <t>Dr. Arun Kumar — Cardiology</t>
+  </si>
+  <si>
+    <t>Routine checkup</t>
+  </si>
+  <si>
+    <t>TN002_sneha_meena_apollo</t>
+  </si>
+  <si>
+    <t>PT-0002 — Sneha Patel</t>
+  </si>
+  <si>
+    <t>Dr. Meena Reddy — Neurology</t>
+  </si>
+  <si>
+    <t>Post-op review</t>
+  </si>
+  <si>
+    <t>TN003_karan_vikram_medicare</t>
+  </si>
+  <si>
+    <t>PT-0007 — Karan Malhotra</t>
+  </si>
+  <si>
+    <t>Dr. Vikram Singh — Orthopedics</t>
+  </si>
+  <si>
+    <t>First visit</t>
+  </si>
+  <si>
+    <t>query</t>
+  </si>
+  <si>
+    <t>expectedResult</t>
+  </si>
+  <si>
+    <t>TD001_search_rajesh</t>
+  </si>
+  <si>
+    <t>Rajesh</t>
+  </si>
+  <si>
+    <t>match</t>
+  </si>
+  <si>
+    <t>TD002_search_sneha</t>
+  </si>
+  <si>
+    <t>Sneha</t>
+  </si>
+  <si>
+    <t>TD003_search_mohan</t>
+  </si>
+  <si>
+    <t>Mohan</t>
+  </si>
+  <si>
+    <t>TD004_search_test_name</t>
+  </si>
+  <si>
+    <t>TD005_search_no_match</t>
+  </si>
+  <si>
+    <t>ZZZNoSuchPatient</t>
+  </si>
+  <si>
+    <t>noMatch</t>
+  </si>
+  <si>
+    <t>TS001_status_all</t>
+  </si>
+  <si>
+    <t>All status</t>
+  </si>
+  <si>
+    <t>TS002_status_pending</t>
+  </si>
+  <si>
+    <t>TS003_status_ready</t>
+  </si>
+  <si>
+    <t>Ready</t>
+  </si>
+  <si>
+    <t>TS004_status_abnormal</t>
+  </si>
+  <si>
+    <t>Abnormal</t>
+  </si>
+  <si>
+    <t>TO001_paracetamol_city</t>
+  </si>
+  <si>
+    <t>Paracetamol 500mg</t>
+  </si>
+  <si>
+    <t>Analgesic</t>
+  </si>
+  <si>
+    <t>Routine stock replenishment</t>
+  </si>
+  <si>
+    <t>TO002_aspirin_apollo</t>
+  </si>
+  <si>
+    <t>Aspirin 75mg</t>
+  </si>
+  <si>
+    <t>Cardiac</t>
+  </si>
+  <si>
+    <t>Cardiac ward stock</t>
+  </si>
+  <si>
+    <t>TO003_metformin_medicare</t>
+  </si>
+  <si>
+    <t>Metformin 500mg</t>
+  </si>
+  <si>
+    <t>Diabetes</t>
+  </si>
+  <si>
+    <t>Monthly refill</t>
+  </si>
+  <si>
+    <t>sessionType</t>
+  </si>
+  <si>
+    <t>TVS001_arun_rajesh</t>
+  </si>
+  <si>
+    <t>Rajesh Sharma</t>
+  </si>
+  <si>
+    <t>Consultation</t>
+  </si>
+  <si>
+    <t>Initial video consult</t>
+  </si>
+  <si>
+    <t>TVS002_meena_sneha</t>
+  </si>
+  <si>
+    <t>Sneha Patel</t>
+  </si>
+  <si>
+    <t>Follow-up review</t>
+  </si>
+  <si>
+    <t>TVS003_vikram_mohan</t>
+  </si>
+  <si>
+    <t>Mohan Das</t>
+  </si>
+  <si>
+    <t>department</t>
+  </si>
+  <si>
+    <t>period</t>
+  </si>
+  <si>
+    <t>TF001_all_all_7d</t>
+  </si>
+  <si>
+    <t>All Hospitals</t>
+  </si>
+  <si>
+    <t>All Departments</t>
+  </si>
+  <si>
+    <t>Last 7 Days</t>
+  </si>
+  <si>
+    <t>TF002_city_cardio_30d</t>
+  </si>
+  <si>
+    <t>Last 30 Days</t>
+  </si>
+  <si>
+    <t>TF003_apollo_peds_90d</t>
+  </si>
+  <si>
+    <t>Pediatrics</t>
+  </si>
+  <si>
+    <t>Last 90 Days</t>
+  </si>
+  <si>
+    <t>TF004_medicare_neuro_year</t>
+  </si>
+  <si>
+    <t>Neurology</t>
+  </si>
+  <si>
+    <t>Last Year</t>
+  </si>
+  <si>
+    <t>TF005_all_ortho_30d</t>
+  </si>
+  <si>
+    <t>Orthopedics</t>
+  </si>
+  <si>
+    <t>TBA001_arun_inperson</t>
+  </si>
+  <si>
+    <t>Cardiology follow-up</t>
+  </si>
+  <si>
+    <t>TBA002_meena_video</t>
+  </si>
+  <si>
+    <t>Video</t>
+  </si>
+  <si>
+    <t>Neurology consultation</t>
+  </si>
+  <si>
+    <t>TBA003_vikram_inperson</t>
+  </si>
+  <si>
+    <t>Knee pain checkup</t>
+  </si>
+  <si>
+    <t>mode</t>
+  </si>
+  <si>
+    <t>TQ001_chip_ldl</t>
+  </si>
+  <si>
+    <t>What is LDL cholesterol?</t>
+  </si>
+  <si>
+    <t>chip</t>
+  </si>
+  <si>
+    <t>TQ002_chip_lower_ldl</t>
+  </si>
+  <si>
+    <t>How to lower LDL naturally?</t>
+  </si>
+  <si>
+    <t>TQ003_chip_statins</t>
+  </si>
+  <si>
+    <t>What are statins?</t>
+  </si>
+  <si>
+    <t>TQ004_chip_ecg</t>
+  </si>
+  <si>
+    <t>Is my ECG result good?</t>
+  </si>
+  <si>
+    <t>TQ005_type_hdl</t>
+  </si>
+  <si>
+    <t>What does HDL mean?</t>
+  </si>
+  <si>
+    <t>TQ006_type_blood_test</t>
+  </si>
+  <si>
+    <t>Explain my blood test results</t>
+  </si>
+  <si>
+    <t>action</t>
+  </si>
+  <si>
+    <t>text</t>
+  </si>
+  <si>
+    <t>TAH001_chip_lipid</t>
+  </si>
+  <si>
+    <t>General Chat</t>
+  </si>
+  <si>
+    <t>Explain my lipid panel results</t>
+  </si>
+  <si>
+    <t>TAH002_chip_ldl</t>
+  </si>
+  <si>
+    <t>What does elevated LDL mean?</t>
+  </si>
+  <si>
+    <t>TAH003_type_cholesterol</t>
+  </si>
+  <si>
+    <t>What are normal cholesterol levels?</t>
+  </si>
+  <si>
+    <t>TAH004_type_symptoms</t>
+  </si>
+  <si>
+    <t>Symptom Checker</t>
+  </si>
+  <si>
+    <t>I have a headache and fever for 2 days</t>
+  </si>
+  <si>
+    <t>TAH005_quick_symptom</t>
+  </si>
+  <si>
+    <t>quickAction</t>
+  </si>
+  <si>
+    <t>TAH006_quick_lab</t>
+  </si>
+  <si>
+    <t>Explain My Lab Report</t>
+  </si>
+  <si>
+    <t>TAH007_common_bp</t>
+  </si>
+  <si>
+    <t>commonQuestion</t>
+  </si>
+  <si>
+    <t>What does my blood pressure reading mean?</t>
+  </si>
+  <si>
+    <t>TAH008_common_diabetes</t>
+  </si>
+  <si>
+    <t>How can I manage my diabetes better?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -101,13 +885,92 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FFCCCCCC"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <color rgb="FFCCCCCC"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9.9"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Display"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Display"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Display"/>
+      <scheme val="major"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF181818"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -123,16 +986,44 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="20" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="18" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -161,13 +1052,13 @@
         <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="145F82"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E87331"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="186C24"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
         <a:srgbClr val="0F9ED5"/>
@@ -187,7 +1078,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="020F0302020204030204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -453,94 +1344,1959 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="525" row="2">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{93769FBC-BD89-43D8-A400-19EA5317165F}">
+  <we:reference id="29673e3c-d826-4f00-92ee-162334a52b1a" version="1.0.0.8" store="EXCatalog" storeType="EXCatalog"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="en-IN" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;eff5b941-b3ba-4721-a211-c86d3c9126c1&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+  <we:extLst>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{D87F86FE-615C-45B5-9D79-34F1136793EB}">
+      <we:containsCustomFunctions/>
+    </a:ext>
+  </we:extLst>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultColWidth="17.140625" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45064D77-1ECE-4918-B525-A4A3B7823F86}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="25.85546875" customWidth="1"/>
+    <col min="1" max="1" width="24.5703125" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15">
+      <c r="A2" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="22" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15">
+      <c r="A3" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15">
+      <c r="A4" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{F9B04F18-6F0A-460D-9D4C-E1FDC5FAD4B4}"/>
+    <hyperlink ref="C2" r:id="rId2" xr:uid="{E9C53956-D335-4749-B73D-E9AE9ADA77B0}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8D8907D-C1D4-4085-BA57-C8F8A8DB6768}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
+  <cols>
+    <col min="1" max="1" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D2">
+        <v>100</v>
+      </c>
+      <c r="E2">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1DC6E31-8F32-4B15-972B-7124E1050FED}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
+  <cols>
+    <col min="1" max="1" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87715164-B4A9-4967-BE68-FEBD691217EB}">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
+  <cols>
+    <col min="1" max="1" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E2" s="7">
+        <v>9876543210</v>
+      </c>
+      <c r="F2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E80DC387-7ADE-42F2-AD04-E9AC427B8F77}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
+  <cols>
+    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>122</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F690F2B1-79B1-42BF-A505-7F79E2849B0D}">
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="D2" s="13">
+        <f>91-44-28293333</f>
+        <v>-28293286</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="F2" s="13">
+        <v>10</v>
+      </c>
+      <c r="G2" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="D3" s="13">
+        <f>91-22-12345678</f>
+        <v>-12345609</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="F3" s="13">
+        <v>50</v>
+      </c>
+      <c r="G3" s="13">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4" s="13">
+        <f>91-11-87654321</f>
+        <v>-87654241</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="F4" s="13">
+        <v>100</v>
+      </c>
+      <c r="G4" s="13">
+        <v>75</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AF51F08-1165-4FE7-8EEB-FC2ECBE25EEA}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="D2" s="15">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="D3" s="15">
+        <v>46175</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="D4" s="15">
+        <v>46176</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="D5" s="15">
+        <v>46177</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="D6" s="15">
+        <v>46178</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8051E0B1-2006-4369-86F3-1390F66661C0}">
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="E2" s="15">
+        <v>46178</v>
+      </c>
+      <c r="F2" s="16">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="H2" s="14" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="E3" s="15">
+        <v>46179</v>
+      </c>
+      <c r="F3" s="16">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="H3" s="14" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="E4" s="15">
+        <v>46180</v>
+      </c>
+      <c r="F4" s="16">
+        <v>0.38541666666666669</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="H4" s="14" t="s">
+        <v>166</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11DF0633-E086-4B1C-AF04-C092DCAD31BB}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>179</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{795696E2-92F2-4CDC-AE00-032B872F1859}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>186</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{752CB497-BCD7-4C16-8370-F86E945F2378}">
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="D2" s="14">
+        <v>100</v>
+      </c>
+      <c r="E2" s="14">
+        <v>20</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="D3" s="14">
+        <v>50</v>
+      </c>
+      <c r="E3" s="14">
+        <v>15</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="D4" s="14">
+        <v>200</v>
+      </c>
+      <c r="E4" s="14">
+        <v>30</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>198</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC5547E1-8265-48F6-A84D-52EAF56CC962}">
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
+  <cols>
+    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" s="4" customFormat="1" ht="14.1">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="8">
+        <v>9876543210</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="10">
+        <v>9123456701</v>
+      </c>
+      <c r="F3" s="11">
+        <v>3121988</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" s="3">
+        <v>9123456702</v>
+      </c>
+      <c r="F4" s="11">
+        <v>3121988</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H4" t="s">
+        <v>37</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" s="3">
+        <v>9123456702</v>
+      </c>
+      <c r="F5" s="11">
+        <v>3121988</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{FC151F78-10B2-4227-BD4C-F0470DA3A6EB}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37DE043B-66A1-4147-9E67-EFA6F115DAAC}">
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
+  <cols>
+    <col min="4" max="4" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="D2" s="15">
+        <v>46183</v>
+      </c>
+      <c r="E2" s="16">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="D3" s="15">
+        <v>46188</v>
+      </c>
+      <c r="E3" s="16">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="D4" s="15">
+        <v>46204</v>
+      </c>
+      <c r="E4" s="16">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>158</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C223998-EE15-42D1-A8B9-A9EBC4B0DB5C}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="29.1">
+      <c r="A1" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>114</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>209</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="43.5">
+      <c r="A2" s="17" t="s">
+        <v>211</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>212</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>213</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="43.5">
+      <c r="A3" s="17" t="s">
+        <v>215</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="43.5">
+      <c r="A4" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="43.5">
+      <c r="A5" s="17" t="s">
+        <v>220</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>221</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="43.5">
+      <c r="A6" s="17" t="s">
+        <v>223</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>212</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>224</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>216</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{244C9E2F-BB4B-4356-8DE7-A9AFDC262B27}">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
+  <cols>
+    <col min="3" max="3" width="9.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" s="18" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="18" t="s">
+        <v>225</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="C2" s="19">
+        <v>46183</v>
+      </c>
+      <c r="D2" s="20">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="18" t="s">
+        <v>227</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="C3" s="19">
+        <v>46188</v>
+      </c>
+      <c r="D3" s="20">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>228</v>
+      </c>
+      <c r="F3" s="18" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="18" t="s">
+        <v>230</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="C4" s="19">
+        <v>46204</v>
+      </c>
+      <c r="D4" s="20">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="F4" s="18" t="s">
+        <v>231</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE8D91C6-E7EE-453C-AC4C-57830FF1CF37}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="18" t="s">
+        <v>233</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>234</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="18" t="s">
+        <v>236</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>237</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="18" t="s">
+        <v>238</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>239</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="18" t="s">
+        <v>240</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>241</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>243</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="18" t="s">
+        <v>244</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>245</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>70</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0643DDCA-DA73-4919-AA7D-447631DA4DA8}">
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>232</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>246</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="18" t="s">
+        <v>248</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>249</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="18" t="s">
+        <v>251</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>249</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>249</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="18" t="s">
+        <v>255</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>256</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="18" t="s">
+        <v>258</v>
+      </c>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18" t="s">
+        <v>259</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="18" t="s">
+        <v>260</v>
+      </c>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18" t="s">
+        <v>259</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18" t="s">
+        <v>263</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="18" t="s">
+        <v>265</v>
+      </c>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18" t="s">
+        <v>263</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>266</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{343A05DF-B2CD-4966-8822-D6A569054FA0}">
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="17.7109375" customWidth="1"/>
+    <col min="6" max="6" width="16.85546875" customWidth="1"/>
+    <col min="7" max="7" width="16.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="C1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
       <c r="G1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="E2">
         <v>9999988888</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="G2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="E3">
         <v>7777766666</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" xr:uid="{3A93D0C5-4754-42C6-ADFA-A8FD44D6C309}"/>
-    <hyperlink ref="D3" r:id="rId2" xr:uid="{E5F349EB-3574-487E-907B-D2E9B920984D}"/>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{01A4B3FE-FAC2-459F-B66E-A6CD4B5018D8}"/>
+    <hyperlink ref="D3" r:id="rId2" xr:uid="{945F4346-8EED-4752-A7B6-3239BCE4BB96}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCEE01AC-69AA-41EC-AB9D-2C17A8F19EE9}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E08C65E8-DE7E-42A4-B37E-94981247A45D}">
+  <dimension ref="A1:K2"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
+  <cols>
+    <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="K1" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="7">
+        <v>9999999999</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="G2">
+        <v>30</v>
+      </c>
+      <c r="H2" s="7">
+        <v>34700</v>
+      </c>
+      <c r="I2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5BE7F55-1345-4108-923B-0A41576493AB}">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
+  <cols>
+    <col min="1" max="1" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="7">
+        <v>46188</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2D9C8C5-C73D-486C-8F51-3D510C42F653}">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
+  <cols>
+    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="33.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E2" s="7">
+        <v>46188</v>
+      </c>
+      <c r="F2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FFAC5E4-BDFE-4DC7-B957-884FFA341B3B}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
+  <cols>
+    <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="31.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="7">
+        <v>46188</v>
+      </c>
+      <c r="D2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97E58940-03EA-43D5-AB8A-F1428AB480A3}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
+  <cols>
+    <col min="1" max="1" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="31.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="7">
+        <v>46188</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2">
+        <v>30</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>